--- a/API_Endpoints_Specification.xlsx
+++ b/API_Endpoints_Specification.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="API Endpoint Specification" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Product &amp; Variant CRUD" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="366">
   <si>
     <t>Billu Bazaar - API Endpoints Specification</t>
   </si>
@@ -1405,12 +1406,1168 @@
   <si>
     <t>Used in admin site settings forms to update store hours, logos, banners, or tags.</t>
   </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Operation Name</t>
+  </si>
+  <si>
+    <t>HTTP Method</t>
+  </si>
+  <si>
+    <t>Endpoint Route</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Headers</t>
+  </si>
+  <si>
+    <t>Request Payload / Query / Params</t>
+  </si>
+  <si>
+    <t>Response Payload (Real DB JSON)</t>
+  </si>
+  <si>
+    <t>Remarks (Where &amp; How It Is Used)</t>
+  </si>
+  <si>
+    <t>Product CRUD</t>
+  </si>
+  <si>
+    <t>List Products (Filtered &amp; Paginated)</t>
+  </si>
+  <si>
+    <t>None (Public Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Query Parameters (Optional):
+{
+  "page": 1,
+  "limit": 20,
+  "search": "Sony",
+  "sort": "createdAt",
+  "order": "DESC",
+  "featured": "true"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "products": [
+    {
+      "defaultProductImage": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+      "images": [
+        "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg"
+      ],
+      "spin_images": [],
+      "tags": [],
+      "attributes": {
+        "Color": "Black"
+      },
+      "dimensions": {
+        "length": "25",
+        "width": "25",
+        "height": "25",
+        "unit": "cm"
+      },
+      "discountPercent": 0,
+      "id": 33,
+      "name": "Sony WH-1000XM5 Wireless Headphones",
+      "slug": "sony-wh-1000xm5-wireless-headphones",
+      "description": "&lt;p data-path-to-node=\"4,1,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,0\" data-index-in-node=\"0\"&gt;Immerse Yourself in Pure Sound&lt;/b&gt;&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,1\"&gt;Experience an unparalleled acoustic journey with the &lt;b data-path-to-node=\"4,1,1,1\" data-index-in-node=\"53\"&gt;Sony WH-1000XM5 Wireless Headphones&lt;/b&gt;. Engineered with two processors and eight microphones, these headphones automatically optimize noise cancellation based on your environment and wearing conditions—delivering distraction-free listening whether you are on a noisy flight or working in a busy cafe.&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,2\"&gt;&lt;b data-path-to-node=\"4,1,1,2\" data-index-in-node=\"0\"&gt;Key Features:&lt;/b&gt;&lt;/p&gt;&lt;ul data-path-to-node=\"4,1,1,3\"&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,0,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,0,0\" data-index-in-node=\"0\"&gt;Industry-Leading Noise Cancellation:&lt;/b&gt; Driven by the HD Noise Cancelling Processor QN1 for unmatched acoustic isolation.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,1,0\" data-index-in-node=\"0\"&gt;Precision Voice Pickup:&lt;/b&gt; Four beamforming microphones isolate your voice for crystal-clear phone calls even in windy or noisy environments.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,2,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,2,0\" data-index-in-node=\"0\"&gt;All-Day Comfort:&lt;/b&gt; Crafted with soft fit leather and a lightweight headband to relieve pressure on your ears.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,3,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,3,0\" data-index-in-node=\"0\"&gt;30-Hour Battery Life:&lt;/b&gt; Quick-charge capabilities give you up to 3 hours of playback with just a 3-minute charge.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,4,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,4,0\" data-index-in-node=\"0\"&gt;Smart Features:&lt;/b&gt; \"Speak-to-Chat\" automatically pauses your audio when you start speaking, letting ambient sound in without touching your headphones.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;",
+      "shortDescription": "Silence the world and elevate your audio. The Sony WH-1000XM5 headphones deliver industry-leading noise cancellation, crystal-clear hands-free calling.",
+      "price": "4500.00",
+      "comparePrice": null,
+      "currency": "INR",
+      "sku": "SKU-SONYWH10",
+      "stock": 252,
+      "categoryId": 1,
+      "subCategoryId": 1,
+      "subSubCategoryId": 1,
+      "vendorId": 8,
+      "showAuthenticity": false,
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "18%",
+      "has360View": false,
+      "hasVideo": false,
+      "videoUrl": "",
+      "model_3d_url": null,
+      "spinImagePath": null,
+      "spinImageCount": 0,
+      "spinImageExt": "jpg",
+      "isFeatured": true,
+      "isNewArrival": true,
+      "isBestSeller": true,
+      "rating": "0.00",
+      "reviewCount": 0,
+      "weight": "25.00",
+      "isActive": true,
+      "seoDescription": null,
+      "createdAt": "2026-07-25T05:36:43.000Z",
+      "updatedAt": "2026-07-25T07:19:10.000Z",
+      "category": {
+        "id": 1,
+        "name": "Electronics &amp; Gadgets",
+        "slug": "electronics-gadgets"
+      },
+      "subcategory": {
+        "id": 1,
+        "name": "Audio",
+        "slug": "electronics-gadgets-audio"
+      },
+      "subsubcategory": {
+        "id": 1,
+        "name": "Headphones",
+        "slug": "electronics-gadgets-audio-headphones"
+      },
+      "vendor": {
+        "id": 8,
+        "name": "sample",
+        "logo": null
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      },
+      "variants": [
+        {
+          "attributes": {
+            "Color": "Black"
+          },
+          "images": [],
+          "id": 9,
+          "sku": "SKU-SONYWH10-BLACK",
+          "price": "4500.00",
+          "mrp": "5000.00",
+          "stock": 250,
+          "image": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "18%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        },
+        {
+          "attributes": {
+            "Color": "silver"
+          },
+          "images": [
+            "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+            "/uploads/others/98bcd1d2-bc4d-43b5-820c-129bac210d9f.jpg",
+            "/uploads/others/2eae9c03-321c-4f9f-bfb9-b3675f46e82a.jpg"
+          ],
+          "id": 10,
+          "sku": "SKU-SONYWH10-SILVER",
+          "price": "45000.00",
+          "mrp": "45000.00",
+          "stock": 2,
+          "image": "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "5%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        }
+      ]
+    },
+    {
+      "defaultProductImage": "/uploads/products/29fc983e-0024-4da3-b0bc-269217224eb3.jpg",
+      "images": [
+        "/uploads/products/29fc983e-0024-4da3-b0bc-269217224eb3.jpg"
+      ],
+      "spin_images": [],
+      "tags": [],
+      "attributes": {
+        "Case": "USB-C Case"
+      },
+      "dimensions": {
+        "length": "25",
+        "width": "25",
+        "height": "36",
+        "unit": "cm"
+      },
+      "discountPercent": 0,
+      "id": 34,
+      "name": "Apple AirPods Max",
+      "slug": "apple-airpods-max",
+      "description": "&lt;p data-path-to-node=\"4,1,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,0\" data-index-in-node=\"0\"&gt;Immerse Yourself in Pure Sound&lt;/b&gt;&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,1\"&gt;Experience an unparalleled acoustic journey with the &lt;b data-path-to-node=\"4,1,1,1\" data-index-in-node=\"53\"&gt;Sony WH-1000XM5 Wireless Headphones&lt;/b&gt;. Engineered with two processors and eight microphones, these headphones automatically optimize noise cancellation based on your environment and wearing conditions—delivering distraction-free listening whether you are on a noisy flight or working in a busy cafe.&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,2\"&gt;&lt;b data-path-to-node=\"4,1,1,2\" data-index-in-node=\"0\"&gt;Key Features:&lt;/b&gt;&lt;/p&gt;&lt;ul data-path-to-node=\"4,1,1,3\"&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,0,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,0,0\" data-index-in-node=\"0\"&gt;Industry-Leading Noise Cancellation:&lt;/b&gt; Driven by the HD Noise Cancelling Processor QN1 for unmatched acoustic isolation.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,1,0\" data-index-in-node=\"0\"&gt;Precision Voice Pickup:&lt;/b&gt; Four beamforming microphones isolate your voice for crystal-clear phone calls even in windy or noisy environments.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,2,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,2,0\" data-index-in-node=\"0\"&gt;All-Day Comfort:&lt;/b&gt; Crafted with soft fit leather and a lightweight headband to relieve pressure on your ears.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,3,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,3,0\" data-index-in-node=\"0\"&gt;30-Hour Battery Life:&lt;/b&gt; Quick-charge capabilities give you up to 3 hours of playback with just a 3-minute charge.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,4,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,4,0\" data-index-in-node=\"0\"&gt;Smart Features:&lt;/b&gt; \"Speak-to-Chat\" automatically pauses your audio when you start speaking, letting ambient sound in without touching your headphones.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;",
+      "shortDescription": "Silence the world and elevate your audio. The Sony WH-1000XM5 headphones deliver industry-leading noise cancellation, crystal-clear hands-free calling, and up to 30 hours of battery life in a ultra-co",
+      "price": "3500.00",
+      "comparePrice": null,
+      "currency": "INR",
+      "sku": "SKU-APPLEAIR",
+      "stock": 30,
+      "categoryId": 1,
+      "subCategoryId": 1,
+      "subSubCategoryId": 2,
+      "vendorId": 8,
+      "showAuthenticity": true,
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "18%",
+      "has360View": false,
+      "hasVideo": false,
+      "videoUrl": "",
+      "model_3d_url": null,
+      "spinImagePath": null,
+      "spinImageCount": 0,
+      "spinImageExt": "jpg",
+      "isFeatured": true,
+      "isNewArrival": true,
+      "isBestSeller": true,
+      "rating": "0.00",
+      "reviewCount": 0,
+      "weight": "20.00",
+      "isActive": true,
+      "seoDescription": null,
+      "createdAt": "2026-07-25T06:02:12.000Z",
+      "updatedAt": "2026-07-25T07:19:10.000Z",
+      "category": {
+        "id": 1,
+        "name": "Electronics &amp; Gadgets",
+        "slug": "electronics-gadgets"
+      },
+      "subcategory": {
+        "id": 1,
+        "name": "Audio",
+        "slug": "electronics-gadgets-audio"
+      },
+      "subsubcategory": {
+        "id": 2,
+        "name": "Earbuds",
+        "slug": "electronics-gadgets-audio-earbuds"
+      },
+      "vendor": {
+        "id": 8,
+        "name": "sample",
+        "logo": null
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      },
+      "variants": [
+        {
+          "attributes": {
+            "Case": "Lightning Case"
+          },
+          "images": [
+            "/uploads/others/33abdb7d-113b-47ee-a2c7-25b8580f2ad8.jpg",
+            "/uploads/others/aac4e8d6-5664-4e16-a659-0e5288186d0e.jpg"
+          ],
+          "id": 12,
+          "sku": "SKU-APPLEAIR-LIGHTNINGCASE",
+          "price": "3500.00",
+          "mrp": "3500.00",
+          "stock": 10,
+          "image": "/uploads/others/33abdb7d-113b-47ee-a2c7-25b8580f2ad8.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "5%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        },
+        {
+          "attributes": {
+            "Case": "USB-C Case"
+          },
+          "images": [],
+          "id": 11,
+          "sku": "SKU-APPLEAIR-USB-CCASE",
+          "price": "4500.00",
+          "mrp": "4500.00",
+          "stock": 20,
+          "image": "/uploads/products/29fc983e-0024-4da3-b0bc-269217224eb3.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "18%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        }
+      ]
+    }
+  ],
+  "total": 3,
+  "page": 1,
+  "totalPages": 1
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Storefront Catalog/Shop Page (/shop), Category Filter Pages, Search Listing, and Admin Product List View (/admin/products).
+• How Used: Fetches paginated products with relational joins (Category, SubCategory, Vendor, Warehouse, Variants). Supports multi-faceted filtering by price, category slug/ID, seller vendor, and featured flags.</t>
+  </si>
+  <si>
+    <t>Get Featured Products</t>
+  </si>
+  <si>
+    <t>No Request Payload or Query Params required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "products": [
+    {
+      "defaultProductImage": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+      "images": [
+        "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg"
+      ],
+      "spin_images": [],
+      "tags": [],
+      "attributes": {
+        "Color": "Black"
+      },
+      "dimensions": {
+        "length": "25",
+        "width": "25",
+        "height": "25",
+        "unit": "cm"
+      },
+      "discountPercent": 0,
+      "id": 33,
+      "name": "Sony WH-1000XM5 Wireless Headphones",
+      "slug": "sony-wh-1000xm5-wireless-headphones",
+      "description": "&lt;p data-path-to-node=\"4,1,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,0\" data-index-in-node=\"0\"&gt;Immerse Yourself in Pure Sound&lt;/b&gt;&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,1\"&gt;Experience an unparalleled acoustic journey with the &lt;b data-path-to-node=\"4,1,1,1\" data-index-in-node=\"53\"&gt;Sony WH-1000XM5 Wireless Headphones&lt;/b&gt;. Engineered with two processors and eight microphones, these headphones automatically optimize noise cancellation based on your environment and wearing conditions—delivering distraction-free listening whether you are on a noisy flight or working in a busy cafe.&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,2\"&gt;&lt;b data-path-to-node=\"4,1,1,2\" data-index-in-node=\"0\"&gt;Key Features:&lt;/b&gt;&lt;/p&gt;&lt;ul data-path-to-node=\"4,1,1,3\"&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,0,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,0,0\" data-index-in-node=\"0\"&gt;Industry-Leading Noise Cancellation:&lt;/b&gt; Driven by the HD Noise Cancelling Processor QN1 for unmatched acoustic isolation.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,1,0\" data-index-in-node=\"0\"&gt;Precision Voice Pickup:&lt;/b&gt; Four beamforming microphones isolate your voice for crystal-clear phone calls even in windy or noisy environments.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,2,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,2,0\" data-index-in-node=\"0\"&gt;All-Day Comfort:&lt;/b&gt; Crafted with soft fit leather and a lightweight headband to relieve pressure on your ears.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,3,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,3,0\" data-index-in-node=\"0\"&gt;30-Hour Battery Life:&lt;/b&gt; Quick-charge capabilities give you up to 3 hours of playback with just a 3-minute charge.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,4,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,4,0\" data-index-in-node=\"0\"&gt;Smart Features:&lt;/b&gt; \"Speak-to-Chat\" automatically pauses your audio when you start speaking, letting ambient sound in without touching your headphones.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;",
+      "shortDescription": "Silence the world and elevate your audio. The Sony WH-1000XM5 headphones deliver industry-leading noise cancellation, crystal-clear hands-free calling.",
+      "price": "4500.00",
+      "comparePrice": null,
+      "currency": "INR",
+      "sku": "SKU-SONYWH10",
+      "stock": 252,
+      "categoryId": 1,
+      "subCategoryId": 1,
+      "subSubCategoryId": 1,
+      "vendorId": 8,
+      "showAuthenticity": false,
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "18%",
+      "has360View": false,
+      "hasVideo": false,
+      "videoUrl": "",
+      "model_3d_url": null,
+      "spinImagePath": null,
+      "spinImageCount": 0,
+      "spinImageExt": "jpg",
+      "isFeatured": true,
+      "isNewArrival": true,
+      "isBestSeller": true,
+      "rating": "0.00",
+      "reviewCount": 0,
+      "weight": "25.00",
+      "isActive": true,
+      "seoDescription": null,
+      "createdAt": "2026-07-25T05:36:43.000Z",
+      "updatedAt": "2026-07-25T07:19:10.000Z",
+      "category": {
+        "id": 1,
+        "name": "Electronics &amp; Gadgets",
+        "slug": "electronics-gadgets"
+      },
+      "subcategory": {
+        "id": 1,
+        "name": "Audio",
+        "slug": "electronics-gadgets-audio"
+      },
+      "subsubcategory": {
+        "id": 1,
+        "name": "Headphones",
+        "slug": "electronics-gadgets-audio-headphones"
+      },
+      "vendor": {
+        "id": 8,
+        "name": "sample",
+        "logo": null
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      },
+      "variants": [
+        {
+          "attributes": {
+            "Color": "Black"
+          },
+          "images": [],
+          "id": 9,
+          "sku": "SKU-SONYWH10-BLACK",
+          "price": "4500.00",
+          "mrp": "5000.00",
+          "stock": 250,
+          "image": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "18%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        },
+        {
+          "attributes": {
+            "Color": "silver"
+          },
+          "images": [
+            "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+            "/uploads/others/98bcd1d2-bc4d-43b5-820c-129bac210d9f.jpg",
+            "/uploads/others/2eae9c03-321c-4f9f-bfb9-b3675f46e82a.jpg"
+          ],
+          "id": 10,
+          "sku": "SKU-SONYWH10-SILVER",
+          "price": "45000.00",
+          "mrp": "45000.00",
+          "stock": 2,
+          "image": "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "5%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        }
+      ]
+    },
+    {
+      "defaultProductImage": "/uploads/products/29fc983e-0024-4da3-b0bc-269217224eb3.jpg",
+      "images": [
+        "/uploads/products/29fc983e-0024-4da3-b0bc-269217224eb3.jpg"
+      ],
+      "spin_images": [],
+      "tags": [],
+      "attributes": {
+        "Case": "USB-C Case"
+      },
+      "dimensions": {
+        "length": "25",
+        "width": "25",
+        "height": "36",
+        "unit": "cm"
+      },
+      "discountPercent": 0,
+      "id": 34,
+      "name": "Apple AirPods Max",
+      "slug": "apple-airpods-max",
+      "description": "&lt;p data-path-to-node=\"4,1,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,0\" data-index-in-node=\"0\"&gt;Immerse Yourself in Pure Sound&lt;/b&gt;&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,1\"&gt;Experience an unparalleled acoustic journey with the &lt;b data-path-to-node=\"4,1,1,1\" data-index-in-node=\"53\"&gt;Sony WH-1000XM5 Wireless Headphones&lt;/b&gt;. Engineered with two processors and eight microphones, these headphones automatically optimize noise cancellation based on your environment and wearing conditions—delivering distraction-free listening whether you are on a noisy flight or working in a busy cafe.&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,2\"&gt;&lt;b data-path-to-node=\"4,1,1,2\" data-index-in-node=\"0\"&gt;Key Features:&lt;/b&gt;&lt;/p&gt;&lt;ul data-path-to-node=\"4,1,1,3\"&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,0,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,0,0\" data-index-in-node=\"0\"&gt;Industry-Leading Noise Cancellation:&lt;/b&gt; Driven by the HD Noise Cancelling Processor QN1 for unmatched acoustic isolation.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,1,0\" data-index-in-node=\"0\"&gt;Precision Voice Pickup:&lt;/b&gt; Four beamforming microphones isolate your voice for crystal-clear phone calls even in windy or noisy environments.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,2,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,2,0\" data-index-in-node=\"0\"&gt;All-Day Comfort:&lt;/b&gt; Crafted with soft fit leather and a lightweight headband to relieve pressure on your ears.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,3,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,3,0\" data-index-in-node=\"0\"&gt;30-Hour Battery Life:&lt;/b&gt; Quick-charge capabilities give you up to 3 hours of playback with just a 3-minute charge.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,4,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,4,0\" data-index-in-node=\"0\"&gt;Smart Features:&lt;/b&gt; \"Speak-to-Chat\" automatically pauses your audio when you start speaking, letting ambient sound in without touching your headphones.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;",
+      "shortDescription": "Silence the world and elevate your audio. The Sony WH-1000XM5 headphones deliver industry-leading noise cancellation, crystal-clear hands-free calling, and up to 30 hours of battery life in a ultra-co",
+      "price": "3500.00",
+      "comparePrice": null,
+      "currency": "INR",
+      "sku": "SKU-APPLEAIR",
+      "stock": 30,
+      "categoryId": 1,
+      "subCategoryId": 1,
+      "subSubCategoryId": 2,
+      "vendorId": 8,
+      "showAuthenticity": true,
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "18%",
+      "has360View": false,
+      "hasVideo": false,
+      "videoUrl": "",
+      "model_3d_url": null,
+      "spinImagePath": null,
+      "spinImageCount": 0,
+      "spinImageExt": "jpg",
+      "isFeatured": true,
+      "isNewArrival": true,
+      "isBestSeller": true,
+      "rating": "0.00",
+      "reviewCount": 0,
+      "weight": "20.00",
+      "isActive": true,
+      "seoDescription": null,
+      "createdAt": "2026-07-25T06:02:12.000Z",
+      "updatedAt": "2026-07-25T07:19:10.000Z",
+      "category": {
+        "id": 1,
+        "name": "Electronics &amp; Gadgets",
+        "slug": "electronics-gadgets"
+      },
+      "subcategory": {
+        "id": 1,
+        "name": "Audio",
+        "slug": "electronics-gadgets-audio"
+      },
+      "subsubcategory": {
+        "id": 2,
+        "name": "Earbuds",
+        "slug": "electronics-gadgets-audio-earbuds"
+      },
+      "vendor": {
+        "id": 8,
+        "name": "sample",
+        "logo": null
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      },
+      "variants": [
+        {
+          "attributes": {
+            "Case": "Lightning Case"
+          },
+          "images": [
+            "/uploads/others/33abdb7d-113b-47ee-a2c7-25b8580f2ad8.jpg",
+            "/uploads/others/aac4e8d6-5664-4e16-a659-0e5288186d0e.jpg"
+          ],
+          "id": 12,
+          "sku": "SKU-APPLEAIR-LIGHTNINGCASE",
+          "price": "3500.00",
+          "mrp": "3500.00",
+          "stock": 10,
+          "image": "/uploads/others/33abdb7d-113b-47ee-a2c7-25b8580f2ad8.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "5%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        },
+        {
+          "attributes": {
+            "Case": "USB-C Case"
+          },
+          "images": [],
+          "id": 11,
+          "sku": "SKU-APPLEAIR-USB-CCASE",
+          "price": "4500.00",
+          "mrp": "4500.00",
+          "stock": 20,
+          "image": "/uploads/products/29fc983e-0024-4da3-b0bc-269217224eb3.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "18%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        }
+      ]
+    },
+    {
+      "defaultProductImage": "/uploads/products/58eea324-c76b-4dc8-b45f-e739fcbf50f7.jpg",
+      "images": [
+        "/uploads/products/58eea324-c76b-4dc8-b45f-e739fcbf50f7.jpg"
+      ],
+      "spin_images": [],
+      "tags": [],
+      "attributes": {
+        "RAM": "8 GB",
+        "SSD": "256GB",
+        "Color": "Black"
+      },
+      "dimensions": {
+        "length": "450",
+        "width": "450",
+        "height": "45",
+        "unit": "cm"
+      },
+      "discountPercent": 0,
+      "id": 35,
+      "name": "Apple MacBook Air 15\" (M3)",
+      "slug": "apple-macbook-air-15-m3",
+      "description": "&lt;p data-path-to-node=\"4,1,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,0\" data-index-in-node=\"0\"&gt;Immerse Yourself in Pure Sound&lt;/b&gt;&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,1\"&gt;Experience an unparalleled acoustic journey with the &lt;b data-path-to-node=\"4,1,1,1\" data-index-in-node=\"53\"&gt;Sony WH-1000XM5 Wireless Headphones&lt;/b&gt;. Engineered with two processors and eight microphones, these headphones automatically optimize noise cancellation based on your environment and wearing conditions—delivering distraction-free listening whether you are on a noisy flight or working in a busy cafe.&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,2\"&gt;&lt;b data-path-to-node=\"4,1,1,2\" data-index-in-node=\"0\"&gt;Key Features:&lt;/b&gt;&lt;/p&gt;&lt;ul data-path-to-node=\"4,1,1,3\"&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,0,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,0,0\" data-index-in-node=\"0\"&gt;Industry-Leading Noise Cancellation:&lt;/b&gt; Driven by the HD Noise Cancelling Processor QN1 for unmatched acoustic isolation.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,1,0\" data-index-in-node=\"0\"&gt;Precision Voice Pickup:&lt;/b&gt; Four beamforming microphones isolate your voice for crystal-clear phone calls even in windy or noisy environments.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,2,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,2,0\" data-index-in-node=\"0\"&gt;All-Day Comfort:&lt;/b&gt; Crafted with soft fit leather and a lightweight headband to relieve pressure on your ears.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,3,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,3,0\" data-index-in-node=\"0\"&gt;30-Hour Battery Life:&lt;/b&gt; Quick-charge capabilities give you up to 3 hours of playback with just a 3-minute charge.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,4,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,4,0\" data-index-in-node=\"0\"&gt;Smart Features:&lt;/b&gt; \"Speak-to-Chat\" automatically pauses your audio when you start speaking, letting ambient sound in without touching your headphones.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;",
+      "shortDescription": "Silence the world and elevate your audio. The Sony WH-1000XM5 headphones deliver industry-leading noise cancellation, crystal-clear hands-free calling, and up to 30 hours of battery life in a ultra-co",
+      "price": "45000.00",
+      "comparePrice": null,
+      "currency": "INR",
+      "sku": "SKU-APPLEMAC",
+      "stock": 40,
+      "categoryId": 1,
+      "subCategoryId": 2,
+      "subSubCategoryId": 5,
+      "vendorId": 8,
+      "showAuthenticity": true,
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "18%",
+      "has360View": false,
+      "hasVideo": false,
+      "videoUrl": "",
+      "model_3d_url": null,
+      "spinImagePath": null,
+      "spinImageCount": 0,
+      "spinImageExt": "jpg",
+      "isFeatured": true,
+      "isNewArrival": true,
+      "isBestSeller": true,
+      "rating": "0.00",
+      "reviewCount": 0,
+      "weight": "450.00",
+      "isActive": true,
+      "seoDescription": null,
+      "createdAt": "2026-07-25T06:21:33.000Z",
+      "updatedAt": "2026-07-25T07:19:10.000Z",
+      "category": {
+        "id": 1,
+        "name": "Electronics &amp; Gadgets",
+        "slug": "electronics-gadgets"
+      },
+      "subcategory": {
+        "id": 2,
+        "name": "Computers &amp; Laptops",
+        "slug": "electronics-gadgets-computers-laptops"
+      },
+      "subsubcategory": {
+        "id": 5,
+        "name": "Laptops",
+        "slug": "electronics-gadgets-computers-laptops-laptops"
+      },
+      "vendor": {
+        "id": 8,
+        "name": "sample",
+        "logo": null
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      },
+      "variants": [
+        {
+          "attributes": {
+            "RAM": "256GB",
+            "SSD": "512GB",
+            "Color": "White"
+          },
+          "images": [
+            "/uploads/others/f4b17cdf-f776-4b9b-bc32-7642194581a8.jpg",
+            "/uploads/others/810d728f-c256-4afb-8e99-58166dda9eed.jpg",
+            "/uploads/others/40441c9b-e03c-4686-ad6b-08f7e6b180f5.jpg",
+            "/uploads/others/203f383f-b1b9-4ace-85f2-71aef0b67181.jpg"
+          ],
+          "id": 14,
+          "sku": "SKU-APPLEMAC-256GB-512GB-WHITE",
+          "price": "45000.00",
+          "mrp": "45000.00",
+          "stock": 20,
+          "image": "/uploads/others/f4b17cdf-f776-4b9b-bc32-7642194581a8.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "5%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        },
+        {
+          "attributes": {
+            "RAM": "8 GB",
+            "SSD": "256GB",
+            "Color": "Black"
+          },
+          "images": [],
+          "id": 13,
+          "sku": "SKU-APPLEMAC-8GB-256GB-BLACK",
+          "price": "450.00",
+          "mrp": "45000.00",
+          "stock": 20,
+          "image": "/uploads/products/58eea324-c76b-4dc8-b45f-e739fcbf50f7.jpg",
+          "warehouseId": 1,
+          "lowStockThreshold": 10,
+          "gstRate": "18%",
+          "warehouse": {
+            "id": 1,
+            "name": "India Fulfillment Warehouse"
+          }
+        }
+      ]
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Storefront Homepage (/) in the "Featured Collection" slider / section.
+• How Used: Retrieves active products from DB flagged with isFeatured = true for promotional homepage showcase.</t>
+  </si>
+  <si>
+    <t>Live Search Products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Query Parameters:
+{
+  "q": "Sony WH-1000XM5"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "products": [
+    {
+      "id": 33,
+      "name": "Sony WH-1000XM5 Wireless Headphones",
+      "slug": "sony-wh-1000xm5-wireless-headphones",
+      "price": "4500.00",
+      "images": [
+        "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg"
+      ],
+      "discountPercent": 0
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Storefront Header Navigation Search Bar.
+• How Used: Executes title string search (Op.like) returning candidate DB products for real-time live preview dropdown.</t>
+  </si>
+  <si>
+    <t>Get Product Price Range</t>
+  </si>
+  <si>
+    <t>No Request Payload required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "minPrice": 450,
+  "maxPrice": 45000
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Storefront Catalog Shop Page (/shop) Filter Sidebar.
+• How Used: Runs direct aggregate SQL query (MIN(price), MAX(price)) on active DB products to dynamically set the price slider range.</t>
+  </si>
+  <si>
+    <t>Get Product Details by Slug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Parameter:
+:slug = "sony-wh-1000xm5-wireless-headphones"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "product": {
+    "defaultProductImage": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+    "images": [
+      "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg"
+    ],
+    "spin_images": [],
+    "tags": [],
+    "attributes": {
+      "Color": "Black"
+    },
+    "dimensions": {
+      "length": "25",
+      "width": "25",
+      "height": "25",
+      "unit": "cm"
+    },
+    "discountPercent": 0,
+    "id": 33,
+    "name": "Sony WH-1000XM5 Wireless Headphones",
+    "slug": "sony-wh-1000xm5-wireless-headphones",
+    "description": "&lt;p data-path-to-node=\"4,1,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,0\" data-index-in-node=\"0\"&gt;Immerse Yourself in Pure Sound&lt;/b&gt;&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,1\"&gt;Experience an unparalleled acoustic journey with the &lt;b data-path-to-node=\"4,1,1,1\" data-index-in-node=\"53\"&gt;Sony WH-1000XM5 Wireless Headphones&lt;/b&gt;. Engineered with two processors and eight microphones, these headphones automatically optimize noise cancellation based on your environment and wearing conditions—delivering distraction-free listening whether you are on a noisy flight or working in a busy cafe.&lt;/p&gt;&lt;p data-path-to-node=\"4,1,1,2\"&gt;&lt;b data-path-to-node=\"4,1,1,2\" data-index-in-node=\"0\"&gt;Key Features:&lt;/b&gt;&lt;/p&gt;&lt;ul data-path-to-node=\"4,1,1,3\"&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,0,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,0,0\" data-index-in-node=\"0\"&gt;Industry-Leading Noise Cancellation:&lt;/b&gt; Driven by the HD Noise Cancelling Processor QN1 for unmatched acoustic isolation.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,1,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,1,0\" data-index-in-node=\"0\"&gt;Precision Voice Pickup:&lt;/b&gt; Four beamforming microphones isolate your voice for crystal-clear phone calls even in windy or noisy environments.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,2,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,2,0\" data-index-in-node=\"0\"&gt;All-Day Comfort:&lt;/b&gt; Crafted with soft fit leather and a lightweight headband to relieve pressure on your ears.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,3,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,3,0\" data-index-in-node=\"0\"&gt;30-Hour Battery Life:&lt;/b&gt; Quick-charge capabilities give you up to 3 hours of playback with just a 3-minute charge.&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p data-path-to-node=\"4,1,1,3,4,0\"&gt;&lt;b data-path-to-node=\"4,1,1,3,4,0\" data-index-in-node=\"0\"&gt;Smart Features:&lt;/b&gt; \"Speak-to-Chat\" automatically pauses your audio when you start speaking, letting ambient sound in without touching your headphones.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;",
+    "shortDescription": "Silence the world and elevate your audio. The Sony WH-1000XM5 headphones deliver industry-leading noise cancellation, crystal-clear hands-free calling.",
+    "price": "4500.00",
+    "comparePrice": null,
+    "currency": "INR",
+    "sku": "SKU-SONYWH10",
+    "stock": 252,
+    "categoryId": 1,
+    "subCategoryId": 1,
+    "subSubCategoryId": 1,
+    "vendorId": 8,
+    "showAuthenticity": false,
+    "warehouseId": 1,
+    "lowStockThreshold": 10,
+    "gstRate": "18%",
+    "has360View": false,
+    "hasVideo": false,
+    "videoUrl": "",
+    "model_3d_url": null,
+    "spinImagePath": null,
+    "spinImageCount": 0,
+    "spinImageExt": "jpg",
+    "isFeatured": true,
+    "isNewArrival": true,
+    "isBestSeller": true,
+    "rating": "0.00",
+    "reviewCount": 0,
+    "weight": "25.00",
+    "isActive": true,
+    "seoDescription": null,
+    "createdAt": "2026-07-25T05:36:43.000Z",
+    "updatedAt": "2026-07-25T07:19:10.000Z",
+    "category": {
+      "id": 1,
+      "name": "Electronics &amp; Gadgets",
+      "slug": "electronics-gadgets"
+    },
+    "subcategory": {
+      "id": 1,
+      "name": "Audio",
+      "slug": "electronics-gadgets-audio"
+    },
+    "subsubcategory": {
+      "id": 1,
+      "name": "Headphones",
+      "slug": "electronics-gadgets-audio-headphones"
+    },
+    "vendor": {
+      "id": 8,
+      "name": "sample",
+      "logo": null
+    },
+    "warehouse": {
+      "id": 1,
+      "name": "India Fulfillment Warehouse"
+    },
+    "variants": [
+      {
+        "attributes": {
+          "Color": "Black"
+        },
+        "images": [],
+        "id": 9,
+        "sku": "SKU-SONYWH10-BLACK",
+        "price": "4500.00",
+        "mrp": "5000.00",
+        "stock": 250,
+        "image": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+        "warehouseId": 1,
+        "lowStockThreshold": 10,
+        "gstRate": "18%",
+        "warehouse": {
+          "id": 1,
+          "name": "India Fulfillment Warehouse"
+        }
+      },
+      {
+        "attributes": {
+          "Color": "silver"
+        },
+        "images": [
+          "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+          "/uploads/others/98bcd1d2-bc4d-43b5-820c-129bac210d9f.jpg",
+          "/uploads/others/2eae9c03-321c-4f9f-bfb9-b3675f46e82a.jpg"
+        ],
+        "id": 10,
+        "sku": "SKU-SONYWH10-SILVER",
+        "price": "45000.00",
+        "mrp": "45000.00",
+        "stock": 2,
+        "image": "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+        "warehouseId": 1,
+        "lowStockThreshold": 10,
+        "gstRate": "5%",
+        "warehouse": {
+          "id": 1,
+          "name": "India Fulfillment Warehouse"
+        }
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Storefront Product Detail Page (PDP) (/product/:slug) &amp; Quick View Modal.
+• How Used: Loads full product metadata from DB including description, images, 360-spin frame sequence, video URL, vendor, warehouse, and associated variants for customer selection.</t>
+  </si>
+  <si>
+    <t>Create Product (Admin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header: Authorization: Bearer &lt;admin_jwt_token&gt;
+Content-Type: multipart/form-data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form-Data Text Fields (Exact Admin Form Fields):
+productName / name: "Sony WH-1000XM5 Wireless Headphones"
+sku: "SKU-SONYWH10"
+price: "4500.00"
+comparePrice: ""
+stock: "252"
+weight: "25.00"
+dimensions: '{"length":"25","width":"25","height":"25","unit":"cm"}'
+categoryId: "1"
+subCategoryId: "1"
+subSubCategoryId: "1"
+vendorId: "8"
+warehouseId: "1"
+isFeatured: "true"
+isNewArrival: "true"
+isBestSeller: "true"
+isActive: "true"
+showAuthenticity: "false"
+has360View: "false"
+hasVideo: "false"
+videoUrl: ""
+tags: '[]'
+attributes: '{"Color":"Black"}'
+variants: '[{"sku":"SKU-SONYWH10-BLACK","price":"4500.00","mrp":"5000.00","stock":250,"lowStockThreshold":10,"gstRate":"18%","attributes":{"Color":"Black"},"warehouseId":1},{"sku":"SKU-SONYWH10-SILVER","price":"45000.00","mrp":"45000.00","stock":2,"lowStockThreshold":10,"gstRate":"5%","attributes":{"Color":"silver"},"warehouseId":1}]'
+Form-Data File Fields:
+• images: [binary product gallery files]
+• defaultProductImage: [binary default thumbnail file]
+• spin_images: [binary 360 spin frame files]
+• video: [binary video clip file]
+• variantGallery_0: [gallery files for variant 0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Product Management (/admin/products -&gt; "Add New Product" Modal/Form).
+• How Used: Inserts product into DB, uploads images, materializes 360-spin frame sequence metadata, creates SKU variants, and initializes warehouse stock entries.</t>
+  </si>
+  <si>
+    <t>Update Product (Admin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Parameter:
+:id = 33
+Form-Data Text Fields (Exact Admin Form Fields):
+productName / name: "Sony WH-1000XM5 Wireless Headphones"
+price: "4500.00"
+stock: "252"
+existingImages: '["/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg"]'
+existingSpinImages: '[]'
+variants: '[{"id":9,"sku":"SKU-SONYWH10-BLACK","price":"4500.00","mrp":"5000.00","stock":250,"lowStockThreshold":10,"gstRate":"18%","attributes":{"Color":"Black"},"warehouseId":1},{"id":10,"sku":"SKU-SONYWH10-SILVER","price":"45000.00","mrp":"45000.00","stock":2,"lowStockThreshold":10,"gstRate":"5%","attributes":{"Color":"silver"},"warehouseId":1}]'
+Form-Data File Fields (Optional):
+• images: [new product gallery image files]
+• spin_images: [new 360 spin frame files]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Product Manager (/admin/products -&gt; "Edit Product" Modal/Form).
+• How Used: Updates product DB fields, deletes unselected local image files, updates or creates nested variants, and syncs warehouse stock.</t>
+  </si>
+  <si>
+    <t>Delete Product (Admin)</t>
+  </si>
+  <si>
+    <t>Header: Authorization: Bearer &lt;admin_jwt_token&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Parameter:
+:id = 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Product Management Table (/admin/products -&gt; "Delete Product" Button).
+• How Used: Executes a database transaction to cascade purge Product, ProductVariants, WarehouseStock, CartItems, Wishlists, Reviews, StockAlerts, OrderItems, InventoryLogs, and unlinks media files from disk.</t>
+  </si>
+  <si>
+    <t>Variant CRUD</t>
+  </si>
+  <si>
+    <t>List All Variants (Admin)</t>
+  </si>
+  <si>
+    <t>/api/variants</t>
+  </si>
+  <si>
+    <t>None (or Admin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "variants": [
+    {
+      "attributes": {
+        "Color": "Black"
+      },
+      "images": [],
+      "id": 9,
+      "productId": 33,
+      "sku": "SKU-SONYWH10-BLACK",
+      "price": "4500.00",
+      "mrp": "5000.00",
+      "stock": 250,
+      "image": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "18%",
+      "createdAt": "2026-07-25T05:36:43.000Z",
+      "updatedAt": "2026-07-25T05:36:43.000Z",
+      "product": {
+        "id": 33,
+        "name": "Sony WH-1000XM5 Wireless Headphones",
+        "slug": "sony-wh-1000xm5-wireless-headphones"
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      }
+    },
+    {
+      "attributes": {
+        "Color": "silver"
+      },
+      "images": [
+        "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+        "/uploads/others/98bcd1d2-bc4d-43b5-820c-129bac210d9f.jpg",
+        "/uploads/others/2eae9c03-321c-4f9f-bfb9-b3675f46e82a.jpg"
+      ],
+      "id": 10,
+      "productId": 33,
+      "sku": "SKU-SONYWH10-SILVER",
+      "price": "45000.00",
+      "mrp": "45000.00",
+      "stock": 2,
+      "image": "/uploads/others/da93f989-180e-4461-94c3-7242dc6c6312.jpg",
+      "warehouseId": 1,
+      "lowStockThreshold": 10,
+      "gstRate": "5%",
+      "createdAt": "2026-07-25T05:40:28.000Z",
+      "updatedAt": "2026-07-25T05:40:36.000Z",
+      "product": {
+        "id": 33,
+        "name": "Sony WH-1000XM5 Wireless Headphones",
+        "slug": "sony-wh-1000xm5-wireless-headphones"
+      },
+      "warehouse": {
+        "id": 1,
+        "name": "India Fulfillment Warehouse"
+      }
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Variant Management Page (/admin/variants).
+• How Used: Fetches real variant records from DB with joined Parent Product and Warehouse details for global SKU inventory control.</t>
+  </si>
+  <si>
+    <t>Get Variants by Product ID</t>
+  </si>
+  <si>
+    <t>/api/variants/product/:productId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Parameter:
+:productId = 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Storefront Product Details Page (PDP) &amp; Quick View Modal.
+• How Used: Retrieves real DB variants for a specific product ID so customers can select variant options (Color, Size) and view updated price, SKU, and stock.</t>
+  </si>
+  <si>
+    <t>Add Variant to Product (Admin)</t>
+  </si>
+  <si>
+    <t>/api/variants/add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header: Authorization: Bearer &lt;admin_jwt_token&gt;
+Content-Type: multipart/form-data / application/json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body / Form-Data Fields (Exact Admin Form Fields):
+{
+  "productId": 33,
+  "sku": "SKU-SONYWH10-BLACK",
+  "price": 4500,
+  "mrp": 5000,
+  "stock": 250,
+  "lowStockThreshold": 10,
+  "gstRate": "18%",
+  "attributes": {
+    "Color": "Black"
+  },
+  "warehouseId": 1,
+  "existingImages": []
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "variant": {
+    "attributes": {
+      "Color": "Black"
+    },
+    "images": [],
+    "id": 9,
+    "productId": 33,
+    "sku": "SKU-SONYWH10-BLACK",
+    "price": "4500.00",
+    "mrp": "5000.00",
+    "stock": 250,
+    "image": "/uploads/products/00dba637-faf6-4521-bda0-345a6d332d4d.jpg",
+    "warehouseId": 1,
+    "lowStockThreshold": 10,
+    "gstRate": "18%",
+    "createdAt": "2026-07-25T05:36:43.000Z",
+    "updatedAt": "2026-07-25T05:36:43.000Z",
+    "product": {
+      "id": 33,
+      "name": "Sony WH-1000XM5 Wireless Headphones",
+      "slug": "sony-wh-1000xm5-wireless-headphones"
+    },
+    "warehouse": {
+      "id": 1,
+      "name": "India Fulfillment Warehouse"
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Variants Page (/admin/variants -&gt; "Add Variant" Modal).
+• How Used: Creates a new variant in DB, validates duplicate attribute combinations, initializes warehouse stock record, logs inventory movement, and recalculates parent product price &amp; aggregated stock.</t>
+  </si>
+  <si>
+    <t>Update Variant (Admin)</t>
+  </si>
+  <si>
+    <t>/api/variants/update/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Parameter:
+:id = 9
+Body / Form-Data Fields (Exact Admin Form Fields):
+{
+  "sku": "SKU-SONYWH10-BLACK",
+  "price": 4500,
+  "mrp": 5000,
+  "stock": 250,
+  "lowStockThreshold": 10,
+  "gstRate": "18%",
+  "attributes": {
+    "Color": "Black"
+  },
+  "warehouseId": 1,
+  "existingImages": []
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Variants Page (/admin/variants -&gt; "Edit Variant" Modal).
+• How Used: Updates variant fields in DB, synchronizes warehouse inventory level, and recalculates parent product stock &amp; price.</t>
+  </si>
+  <si>
+    <t>Delete Variant (Admin)</t>
+  </si>
+  <si>
+    <t>/api/variants/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Parameter:
+:id = 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "message": "Variant deleted successfully"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where Used: Admin Panel Variants Page (/admin/variants -&gt; "Delete Variant" Action).
+• How Used: Deletes specified variant from DB, purges linked warehouse stock entries, and triggers a sync on the parent product to update remaining total stock and lowest price.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1448,12 +2605,12 @@
     <font>
       <b/>
       <color rgb="2C3E50"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Consolas"/>
     </font>
     <font>
       <color rgb="333333"/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -1474,8 +2631,31 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF003366"/>
+      <sz val="9.5"/>
+      <name val="Consolas"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1507,8 +2687,38 @@
         <fgColor rgb="FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1546,11 +2756,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1579,6 +2819,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3427,6 +4688,433 @@
     <mergeCell ref="A1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="9" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="13" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" ht="160" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="13">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>